--- a/data/excel/21-kinmen.xlsx
+++ b/data/excel/21-kinmen.xlsx
@@ -872,7 +872,6 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1273,8 +1272,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -1297,6 +1302,438 @@
           <t>note</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>金城鎮</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>金城市區</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>金城鎮</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>金城老街</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>金城鎮</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>莒光路商圈</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>金城鎮</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>水頭碼頭</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>金湖鎮</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>金湖市區</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>金湖鎮</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>太湖</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>金湖鎮</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>山外老街</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>金湖鎮</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>瓊林聚落</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>金沙鎮</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>金沙市區</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>金沙鎮</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>沙美老街</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>金沙鎮</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>馬山觀測站</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>金沙鎮</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>蔡厝</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>金寧鄉</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金寧市區</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>金寧鄉</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>古寧頭</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>金寧鄉</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>湖下聚落</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>金寧鄉</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>慈湖</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>烈嶼鄉</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>小金門市區</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>烈嶼鄉</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>黃厝</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>烈嶼鄉</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>九宮坑道</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>烈嶼鄉</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>林湖路</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>烏坵鄉</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>大坵島</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>烏坵鄉</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>小坵島</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>烏坵鄉</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>烏坵燈塔</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>烏坵鄉</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>軍事碉堡</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>商圈</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
